--- a/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,12 +662,101 @@
           <t>NSE:LODHA26AUG1240CE</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-20 12:36:57</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2216</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2220</v>
+      </c>
+      <c r="I3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="K3" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="L3" t="n">
+        <v>43.95</v>
+      </c>
+      <c r="M3" t="n">
+        <v>53.22</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1968</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="S3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>57.02</v>
+      </c>
+      <c r="U3" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>NSE:HYUNDAI26AUG2220CE</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
@@ -751,12 +751,11 @@
           <t>NSE:HYUNDAI26AUG2220CE</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-20 12:38:36</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -756,6 +756,101 @@
           <t>2026-08-20 12:38:36</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:07:49</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>398.85</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>400</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20408</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="S4" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>59.36</v>
+      </c>
+      <c r="U4" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>NSE:KOTAKBANK26AUG400CE</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
@@ -662,6 +662,11 @@
           <t>NSE:LODHA26AUG1240CE</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:28:56</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -845,12 +850,11 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:28:56</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
@@ -662,11 +662,6 @@
           <t>NSE:LODHA26AUG1240CE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-08-20 13:28:56</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -850,11 +845,7 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2026-08-20 13:28:56</t>
-        </is>
-      </c>
+      <c r="AC4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -845,7 +845,101 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:44:11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2217.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2220</v>
+      </c>
+      <c r="I5" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="K5" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="L5" t="n">
+        <v>43.95</v>
+      </c>
+      <c r="M5" t="n">
+        <v>53.22</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1968</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="S5" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="T5" t="n">
+        <v>57.26</v>
+      </c>
+      <c r="U5" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>NSE:HYUNDAI26AUG2220CE</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
@@ -934,12 +934,11 @@
           <t>NSE:HYUNDAI26AUG2220CE</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:49:05</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
@@ -934,11 +934,7 @@
           <t>NSE:HYUNDAI26AUG2220CE</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-08-20 13:49:05</t>
-        </is>
-      </c>
+      <c r="AC5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
@@ -934,7 +934,11 @@
           <t>NSE:HYUNDAI26AUG2220CE</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-08-20 14:08:38</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
@@ -934,11 +934,7 @@
           <t>NSE:HYUNDAI26AUG2220CE</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-08-20 14:08:38</t>
-        </is>
-      </c>
+      <c r="AC5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -934,7 +934,101 @@
           <t>NSE:HYUNDAI26AUG2220CE</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-20 14:27:20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>510.75</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="H6" t="n">
+        <v>510</v>
+      </c>
+      <c r="I6" t="n">
+        <v>10</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="K6" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="M6" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="S6" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="U6" t="n">
+        <v>27</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>NSE:LICHSGFIN26AUG510PE</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1023,12 +1023,101 @@
           <t>NSE:LICHSGFIN26AUG510PE</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-20 14:56:32</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>14824</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>14750</v>
+      </c>
+      <c r="I7" t="n">
+        <v>235.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>122.78</v>
+      </c>
+      <c r="K7" t="n">
+        <v>335.96</v>
+      </c>
+      <c r="L7" t="n">
+        <v>396.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>476.74</v>
+      </c>
+      <c r="N7" t="n">
+        <v>212</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="S7" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>66.70999999999999</v>
+      </c>
+      <c r="U7" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>NSE:DIXON26AUG14750CE</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
@@ -1023,6 +1023,16 @@
           <t>NSE:LICHSGFIN26AUG510PE</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:01:06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1112,12 +1122,6 @@
           <t>NSE:DIXON26AUG14750CE</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,9 +1028,14 @@
           <t>2026-08-20 15:01:06</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:07:06</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
     </row>
@@ -1122,6 +1127,190 @@
           <t>NSE:DIXON26AUG14750CE</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:07:22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>363.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-2.92</v>
+      </c>
+      <c r="H8" t="n">
+        <v>365</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="N8" t="n">
+        <v>13888</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="S8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="U8" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NSE:PFC26AUG365PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:07:22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>3114.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3100</v>
+      </c>
+      <c r="I9" t="n">
+        <v>53.65</v>
+      </c>
+      <c r="J9" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.12</v>
+      </c>
+      <c r="L9" t="n">
+        <v>102.41</v>
+      </c>
+      <c r="M9" t="n">
+        <v>126.79</v>
+      </c>
+      <c r="N9" t="n">
+        <v>931</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="S9" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>72.45999999999999</v>
+      </c>
+      <c r="U9" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>NSE:MCX26AUG3100CE</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
@@ -845,6 +845,11 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:12:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1305,12 +1310,6 @@
           <t>NSE:MCX26AUG3100CE</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
@@ -845,11 +845,7 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2026-08-20 15:12:00</t>
-        </is>
-      </c>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
@@ -845,7 +845,11 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:15:30</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/signals_2026-08-20.xlsx
@@ -662,6 +662,11 @@
           <t>NSE:LODHA26AUG1240CE</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Closed down ~15.4 (-26.8% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -751,6 +756,11 @@
           <t>NSE:HYUNDAI26AUG2220CE</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Closed down ~24.55 (-3.4% from entry)</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>2026-08-20 12:38:36</t>
@@ -845,6 +855,11 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Closed down ~2.05 (-16.3% from entry)</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>2026-08-20 15:15:30</t>
@@ -939,6 +954,11 @@
           <t>NSE:HYUNDAI26AUG2220CE</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Closed up ~28.85 (+13.6% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1132,6 +1152,11 @@
           <t>NSE:DIXON26AUG14750CE</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Closed up ~240.8 (+2.3% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1221,6 +1246,11 @@
           <t>NSE:PFC26AUG365PE</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Closed up ~3.7 (+2.8% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1308,6 +1338,11 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>NSE:MCX26AUG3100CE</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Closed up ~62.0 (+15.6% from entry, EOD estimate)</t>
         </is>
       </c>
     </row>
